--- a/output/pdf_financials_xlsx/BLTC.P.xlsx
+++ b/output/pdf_financials_xlsx/BLTC.P.xlsx
@@ -841,16 +841,16 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.031963</v>
+        <v>-0.031963</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.207435</v>
+        <v>-0.207435</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.203732</v>
+        <v>-0.203732</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.051055</v>
+        <v>-0.051055</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>-0.027277</v>
@@ -981,16 +981,16 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.031963</v>
+        <v>-0.031963</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.207435</v>
+        <v>-0.207435</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.203732</v>
+        <v>-0.203732</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.051055</v>
+        <v>-0.051055</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>-0.027277</v>
@@ -1065,16 +1065,16 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.031963</v>
+        <v>-0.031963</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.207435</v>
+        <v>-0.207435</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.203732</v>
+        <v>-0.203732</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.051055</v>
+        <v>-0.051055</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>-0.027277</v>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-2.07435</v>
+        <v>2.07435</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-10.1866</v>
+        <v>10.1866</v>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
@@ -1191,16 +1191,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.031963</v>
+        <v>-0.031963</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.207435</v>
+        <v>-0.207435</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.203732</v>
+        <v>-0.203732</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.051055</v>
+        <v>-0.051055</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-0.027277</v>
@@ -1247,16 +1247,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.031963</v>
+        <v>-0.031963</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.207435</v>
+        <v>-0.207435</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.203732</v>
+        <v>-0.203732</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.051055</v>
+        <v>-0.051055</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.027277</v>
@@ -1317,16 +1317,16 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0</v>
@@ -3134,7 +3134,7 @@
         <v>0.030704</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.030704</v>
       </c>
     </row>
     <row r="93">
@@ -4686,7 +4686,11 @@
           <t>Reserves (Note 4)</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>
@@ -7531,16 +7535,16 @@
         </is>
       </c>
       <c r="F65" s="5" t="n">
-        <v>0.207435</v>
+        <v>-0.207435</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.203732</v>
+        <v>-0.203732</v>
       </c>
       <c r="H65" s="5" t="n">
-        <v>0.051055</v>
+        <v>-0.051055</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>0.027277</v>
+        <v>-0.027277</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -8820,10 +8824,10 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>0.031963</v>
+        <v>-0.031963</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>0.207435</v>
+        <v>-0.207435</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/BLTC.P.xlsx
+++ b/output/pdf_financials_xlsx/BLTC.P.xlsx
@@ -1394,25 +1394,25 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.32706</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.505221</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.455087</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.294497</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.270738</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.145209</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.100329</v>
       </c>
     </row>
     <row r="35">
@@ -1450,25 +1450,25 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.32706</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.505221</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.455087</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.294497</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.270738</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.145209</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.100329</v>
       </c>
     </row>
     <row r="37">
@@ -1786,25 +1786,25 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.33706</v>
+        <v>0.01</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.505221</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.455087</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.294497</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.270738</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.145628</v>
+        <v>0.000419</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.100329</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/BLTC.P.xlsx
+++ b/output/pdf_financials_xlsx/BLTC.P.xlsx
@@ -5613,7 +5613,11 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="n">
         <v>0.35</v>
       </c>
